--- a/20260513_银河.xlsx
+++ b/20260513_银河.xlsx
@@ -532,13 +532,13 @@
         <v>1000ETF</v>
       </c>
       <c r="C2" s="1">
-        <v>707.2</v>
+        <v>717.8</v>
       </c>
       <c r="D2" s="1">
-        <v>-0.8</v>
+        <v>9.8</v>
       </c>
       <c r="E2" s="2">
-        <v>-0.0011</v>
+        <v>0.0138</v>
       </c>
       <c r="F2" t="str">
         <v/>
@@ -553,28 +553,28 @@
         <v/>
       </c>
       <c r="J2" s="1">
-        <v>-3.9</v>
+        <v>6.7</v>
       </c>
       <c r="K2" s="2">
-        <v>-0.0055</v>
+        <v>0.0094</v>
       </c>
       <c r="L2" s="1">
-        <v>-3.9</v>
+        <v>6.7</v>
       </c>
       <c r="M2" s="2">
-        <v>-0.0055</v>
+        <v>0.0094</v>
       </c>
       <c r="N2" s="1">
-        <v>-3.1</v>
+        <v>5.9</v>
       </c>
       <c r="O2" s="1">
-        <v>-2.9</v>
+        <v>5.9</v>
       </c>
       <c r="P2" s="1">
-        <v>-2.9</v>
+        <v>5.9</v>
       </c>
       <c r="Q2" s="2">
-        <v>0.0237</v>
+        <v>0.024</v>
       </c>
       <c r="R2" s="3">
         <v>200</v>
@@ -583,28 +583,28 @@
         <v>3</v>
       </c>
       <c r="T2" s="2">
-        <v>-0.0011</v>
+        <v>0.0138</v>
       </c>
       <c r="U2" s="5">
-        <v>3.536</v>
+        <v>3.589</v>
       </c>
       <c r="V2" s="5">
         <v>3.556</v>
       </c>
       <c r="W2" s="2">
-        <v>0.0057</v>
+        <v/>
       </c>
       <c r="X2" s="2">
-        <v>0.1047</v>
+        <v>0.1212</v>
       </c>
       <c r="Y2" s="2">
-        <v>0.06</v>
+        <v>0.0759</v>
       </c>
       <c r="Z2" s="2">
-        <v>0.18</v>
+        <v>0.1977</v>
       </c>
       <c r="AA2" s="2">
-        <v>0.4488</v>
+        <v>0.4705</v>
       </c>
     </row>
     <row r="3">
@@ -615,13 +615,13 @@
         <v>豆粕ETF</v>
       </c>
       <c r="C3" s="1">
-        <v>867.6</v>
+        <v>862.8</v>
       </c>
       <c r="D3" s="1">
-        <v>5.6</v>
+        <v>0.8</v>
       </c>
       <c r="E3" s="2">
-        <v>0.0065</v>
+        <v>0.0009</v>
       </c>
       <c r="F3" t="str">
         <v/>
@@ -636,28 +636,28 @@
         <v/>
       </c>
       <c r="J3" s="1">
-        <v>4.7</v>
+        <v>-0.1</v>
       </c>
       <c r="K3" s="2">
-        <v>0.0054</v>
+        <v>-0.0001</v>
       </c>
       <c r="L3" s="1">
-        <v>4.7</v>
+        <v>-0.1</v>
       </c>
       <c r="M3" s="2">
-        <v>0.0054</v>
+        <v>-0.0001</v>
       </c>
       <c r="N3" s="1">
-        <v>5.1</v>
+        <v>-0.9</v>
       </c>
       <c r="O3" s="1">
-        <v>4.3</v>
+        <v>-0.9</v>
       </c>
       <c r="P3" s="1">
-        <v>4.3</v>
+        <v>-0.9</v>
       </c>
       <c r="Q3" s="2">
-        <v>0.0291</v>
+        <v>0.0289</v>
       </c>
       <c r="R3" s="3">
         <v>400</v>
@@ -666,10 +666,10 @@
         <v>3</v>
       </c>
       <c r="T3" s="2">
-        <v>0.0065</v>
+        <v>0.0009</v>
       </c>
       <c r="U3" s="5">
-        <v>2.169</v>
+        <v>2.157</v>
       </c>
       <c r="V3" s="5">
         <v>2.157</v>
@@ -678,16 +678,16 @@
         <v/>
       </c>
       <c r="X3" s="2">
-        <v>0.0418</v>
+        <v>0.0361</v>
       </c>
       <c r="Y3" s="2">
-        <v>0.0905</v>
+        <v>0.0845</v>
       </c>
       <c r="Z3" s="2">
-        <v>0.0982</v>
+        <v>0.0921</v>
       </c>
       <c r="AA3" s="2">
-        <v>0.1362</v>
+        <v>0.1299</v>
       </c>
     </row>
     <row r="4">
@@ -698,13 +698,13 @@
         <v>港股科技</v>
       </c>
       <c r="C4" s="1">
-        <v>728.2</v>
+        <v>734.8</v>
       </c>
       <c r="D4" s="1">
-        <v>-4.4</v>
+        <v>2.2</v>
       </c>
       <c r="E4" s="2">
-        <v>-0.006</v>
+        <v>0.003</v>
       </c>
       <c r="F4" t="str">
         <v/>
@@ -719,28 +719,28 @@
         <v/>
       </c>
       <c r="J4" s="1">
-        <v>-8.9</v>
+        <v>-2.3</v>
       </c>
       <c r="K4" s="2">
-        <v>-0.0121</v>
+        <v>-0.0031</v>
       </c>
       <c r="L4" s="1">
-        <v>-8.9</v>
+        <v>-2.3</v>
       </c>
       <c r="M4" s="2">
-        <v>-0.0121</v>
+        <v>-0.0031</v>
       </c>
       <c r="N4" s="1">
-        <v>-10</v>
+        <v>-2.3</v>
       </c>
       <c r="O4" s="1">
-        <v>-8.9</v>
+        <v>-2.3</v>
       </c>
       <c r="P4" s="1">
-        <v>-8.9</v>
+        <v>-2.3</v>
       </c>
       <c r="Q4" s="2">
-        <v>0.0244</v>
+        <v>0.0246</v>
       </c>
       <c r="R4" s="3">
         <v>1100</v>
@@ -749,28 +749,28 @@
         <v>3</v>
       </c>
       <c r="T4" s="2">
-        <v>-0.006</v>
+        <v>0.003</v>
       </c>
       <c r="U4" s="5">
-        <v>0.662</v>
+        <v>0.668</v>
       </c>
       <c r="V4" s="5">
         <v>0.67</v>
       </c>
       <c r="W4" s="2">
-        <v>0.0121</v>
+        <v>0.003</v>
       </c>
       <c r="X4" s="2">
-        <v>0.0312</v>
+        <v>0.0405</v>
       </c>
       <c r="Y4" s="2">
-        <v>-0.0881</v>
+        <v>-0.0798</v>
       </c>
       <c r="Z4" s="2">
-        <v>-0.1937</v>
+        <v>-0.1864</v>
       </c>
       <c r="AA4" s="2">
-        <v>-0.1054</v>
+        <v>-0.0973</v>
       </c>
     </row>
     <row r="5">
@@ -781,13 +781,13 @@
         <v>300ETF</v>
       </c>
       <c r="C5" s="1">
-        <v>991.8</v>
+        <v>997.4</v>
       </c>
       <c r="D5" s="1">
-        <v>-0.8</v>
+        <v>4.8</v>
       </c>
       <c r="E5" s="2">
-        <v>-0.0008</v>
+        <v>0.0048</v>
       </c>
       <c r="F5" t="str">
         <v/>
@@ -802,28 +802,28 @@
         <v/>
       </c>
       <c r="J5" s="1">
-        <v>0.5</v>
+        <v>6.1</v>
       </c>
       <c r="K5" s="2">
-        <v>0.0005</v>
+        <v>0.0062</v>
       </c>
       <c r="L5" s="1">
-        <v>0.5</v>
+        <v>6.1</v>
       </c>
       <c r="M5" s="2">
-        <v>0.0005</v>
+        <v>0.0062</v>
       </c>
       <c r="N5" s="1">
-        <v>0.5</v>
+        <v>5.9</v>
       </c>
       <c r="O5" s="1">
-        <v>0.3</v>
+        <v>5.9</v>
       </c>
       <c r="P5" s="1">
-        <v>0.3</v>
+        <v>5.9</v>
       </c>
       <c r="Q5" s="2">
-        <v>0.0333</v>
+        <v>0.0334</v>
       </c>
       <c r="R5" s="3">
         <v>200</v>
@@ -832,10 +832,10 @@
         <v>3</v>
       </c>
       <c r="T5" s="2">
-        <v>-0.0008</v>
+        <v>0.0048</v>
       </c>
       <c r="U5" s="5">
-        <v>4.959</v>
+        <v>4.987</v>
       </c>
       <c r="V5" s="5">
         <v>4.957</v>
@@ -844,16 +844,16 @@
         <v/>
       </c>
       <c r="X5" s="2">
-        <v>0.0683</v>
+        <v>0.0744</v>
       </c>
       <c r="Y5" s="2">
-        <v>0.0491</v>
+        <v>0.055</v>
       </c>
       <c r="Z5" s="2">
-        <v>0.0677</v>
+        <v>0.0738</v>
       </c>
       <c r="AA5" s="2">
-        <v>0.3039</v>
+        <v>0.3113</v>
       </c>
     </row>
     <row r="6">
@@ -864,13 +864,13 @@
         <v>黄金ETF</v>
       </c>
       <c r="C6" s="1">
-        <v>981.1</v>
+        <v>979.9</v>
       </c>
       <c r="D6" s="1">
-        <v>0.5</v>
+        <v>-0.7</v>
       </c>
       <c r="E6" s="2">
-        <v>0.0005</v>
+        <v>-0.0007</v>
       </c>
       <c r="F6" t="str">
         <v/>
@@ -885,28 +885,28 @@
         <v/>
       </c>
       <c r="J6" s="1">
-        <v>7.4</v>
+        <v>6.2</v>
       </c>
       <c r="K6" s="2">
-        <v>0.0076</v>
+        <v>0.0064</v>
       </c>
       <c r="L6" s="1">
-        <v>7.4</v>
+        <v>6.2</v>
       </c>
       <c r="M6" s="2">
-        <v>0.0076</v>
+        <v>0.0064</v>
       </c>
       <c r="N6" s="1">
-        <v>7.4</v>
+        <v>6.1</v>
       </c>
       <c r="O6" s="1">
-        <v>7.6</v>
+        <v>6.1</v>
       </c>
       <c r="P6" s="1">
-        <v>7.6</v>
+        <v>6.1</v>
       </c>
       <c r="Q6" s="2">
-        <v>0.0329</v>
+        <v>0.0328</v>
       </c>
       <c r="R6" s="3">
         <v>100</v>
@@ -915,10 +915,10 @@
         <v>3</v>
       </c>
       <c r="T6" s="2">
-        <v>0.0005</v>
+        <v>-0.0007</v>
       </c>
       <c r="U6" s="5">
-        <v>9.811</v>
+        <v>9.799</v>
       </c>
       <c r="V6" s="5">
         <v>9.737</v>
@@ -927,16 +927,16 @@
         <v/>
       </c>
       <c r="X6" s="2">
-        <v>-0.0161</v>
+        <v>-0.0173</v>
       </c>
       <c r="Y6" s="2">
-        <v>-0.0848</v>
+        <v>-0.086</v>
       </c>
       <c r="Z6" s="2">
-        <v>0.0867</v>
+        <v>0.0853</v>
       </c>
       <c r="AA6" s="2">
-        <v>0.3301</v>
+        <v>0.3285</v>
       </c>
     </row>
     <row r="7">
@@ -989,7 +989,7 @@
         <v>2.55</v>
       </c>
       <c r="Q7" s="2">
-        <v>0.1014</v>
+        <v>0.1012</v>
       </c>
       <c r="R7" s="3">
         <v>2700</v>
@@ -1030,13 +1030,13 @@
         <v>创业板</v>
       </c>
       <c r="C8" s="1">
-        <v>787.2</v>
+        <v>803.2</v>
       </c>
       <c r="D8" s="1">
-        <v>-0.8</v>
+        <v>15.2</v>
       </c>
       <c r="E8" s="2">
-        <v>-0.001</v>
+        <v>0.0193</v>
       </c>
       <c r="F8" t="str">
         <v/>
@@ -1051,28 +1051,28 @@
         <v/>
       </c>
       <c r="J8" s="1">
-        <v>0.5</v>
+        <v>16.5</v>
       </c>
       <c r="K8" s="2">
-        <v>0.0006</v>
+        <v>0.021</v>
       </c>
       <c r="L8" s="1">
-        <v>0.5</v>
+        <v>16.5</v>
       </c>
       <c r="M8" s="2">
-        <v>0.0006</v>
+        <v>0.021</v>
       </c>
       <c r="N8" s="1">
-        <v>0.5</v>
+        <v>15.1</v>
       </c>
       <c r="O8" s="1">
-        <v>0.1</v>
+        <v>15.1</v>
       </c>
       <c r="P8" s="1">
-        <v>0.1</v>
+        <v>15.1</v>
       </c>
       <c r="Q8" s="2">
-        <v>0.0264</v>
+        <v>0.0269</v>
       </c>
       <c r="R8" s="3">
         <v>200</v>
@@ -1081,10 +1081,10 @@
         <v>3</v>
       </c>
       <c r="T8" s="2">
-        <v>-0.001</v>
+        <v>0.0193</v>
       </c>
       <c r="U8" s="5">
-        <v>3.936</v>
+        <v>4.016</v>
       </c>
       <c r="V8" s="5">
         <v>3.934</v>
@@ -1093,16 +1093,16 @@
         <v/>
       </c>
       <c r="X8" s="2">
-        <v>0.1451</v>
+        <v>0.1684</v>
       </c>
       <c r="Y8" s="2">
-        <v>0.1859</v>
+        <v>0.21</v>
       </c>
       <c r="Z8" s="2">
-        <v>0.2664</v>
+        <v>0.2922</v>
       </c>
       <c r="AA8" s="2">
-        <v>0.9322</v>
+        <v>0.9715</v>
       </c>
     </row>
     <row r="9">
@@ -1113,13 +1113,13 @@
         <v>转债ETF</v>
       </c>
       <c r="C9" s="1">
-        <v>20151.6</v>
+        <v>20190.8</v>
       </c>
       <c r="D9" s="1">
-        <v>2.8</v>
+        <v>42</v>
       </c>
       <c r="E9" s="2">
-        <v>0.0001</v>
+        <v>0.0021</v>
       </c>
       <c r="F9" t="str">
         <v/>
@@ -1134,28 +1134,28 @@
         <v/>
       </c>
       <c r="J9" s="1">
-        <v>-226.04</v>
+        <v>-186.84</v>
       </c>
       <c r="K9" s="2">
-        <v>-0.0111</v>
+        <v>-0.0092</v>
       </c>
       <c r="L9" s="1">
-        <v>-226.04</v>
+        <v>-186.84</v>
       </c>
       <c r="M9" s="2">
-        <v>-0.0111</v>
+        <v>-0.0092</v>
       </c>
       <c r="N9" s="1">
-        <v>-248.44</v>
+        <v>-186.84</v>
       </c>
       <c r="O9" s="1">
-        <v>-237.24</v>
+        <v>-186.84</v>
       </c>
       <c r="P9" s="1">
-        <v>-237.24</v>
+        <v>-186.84</v>
       </c>
       <c r="Q9" s="2">
-        <v>0.6765</v>
+        <v>0.6763</v>
       </c>
       <c r="R9" s="3">
         <v>1400</v>
@@ -1164,28 +1164,28 @@
         <v>3</v>
       </c>
       <c r="T9" s="2">
-        <v>0.0001</v>
+        <v>0.0021</v>
       </c>
       <c r="U9" s="5">
-        <v>14.394</v>
+        <v>14.422</v>
       </c>
       <c r="V9" s="5">
         <v>14.555</v>
       </c>
       <c r="W9" s="2">
-        <v>0.0112</v>
+        <v>0.0092</v>
       </c>
       <c r="X9" s="2">
-        <v>0.0296</v>
+        <v>0.0316</v>
       </c>
       <c r="Y9" s="2">
-        <v>-0.0207</v>
+        <v>-0.0188</v>
       </c>
       <c r="Z9" s="2">
-        <v>0.0579</v>
+        <v>0.06</v>
       </c>
       <c r="AA9" s="2">
-        <v>0.1959</v>
+        <v>0.1982</v>
       </c>
     </row>
     <row r="10">
@@ -1196,13 +1196,13 @@
         <v>能源化工</v>
       </c>
       <c r="C10" s="1">
-        <v>662</v>
+        <v>657.2</v>
       </c>
       <c r="D10" s="1">
-        <v>-4.8</v>
+        <v>-9.6</v>
       </c>
       <c r="E10" s="2">
-        <v>-0.0072</v>
+        <v>-0.0144</v>
       </c>
       <c r="F10" t="str">
         <v/>
@@ -1217,28 +1217,28 @@
         <v/>
       </c>
       <c r="J10" s="1">
-        <v>-10.1</v>
+        <v>-14.9</v>
       </c>
       <c r="K10" s="2">
-        <v>-0.015</v>
+        <v>-0.0222</v>
       </c>
       <c r="L10" s="1">
-        <v>-10.1</v>
+        <v>-14.9</v>
       </c>
       <c r="M10" s="2">
-        <v>-0.015</v>
+        <v>-0.0222</v>
       </c>
       <c r="N10" s="1">
-        <v>-10.5</v>
+        <v>-14.5</v>
       </c>
       <c r="O10" s="1">
-        <v>-10.5</v>
+        <v>-14.5</v>
       </c>
       <c r="P10" s="1">
-        <v>-10.5</v>
+        <v>-14.5</v>
       </c>
       <c r="Q10" s="2">
-        <v>0.0222</v>
+        <v>0.022</v>
       </c>
       <c r="R10" s="3">
         <v>400</v>
@@ -1247,28 +1247,28 @@
         <v>3</v>
       </c>
       <c r="T10" s="2">
-        <v>-0.0072</v>
+        <v>-0.0144</v>
       </c>
       <c r="U10" s="5">
-        <v>1.655</v>
+        <v>1.643</v>
       </c>
       <c r="V10" s="5">
         <v>1.68</v>
       </c>
       <c r="W10" s="2">
-        <v>0.0151</v>
+        <v>0.0225</v>
       </c>
       <c r="X10" s="2">
-        <v>0.0248</v>
+        <v>0.0173</v>
       </c>
       <c r="Y10" s="2">
-        <v>0.2909</v>
+        <v>0.2816</v>
       </c>
       <c r="Z10" s="2">
-        <v>0.3499</v>
+        <v>0.3401</v>
       </c>
       <c r="AA10" s="2">
-        <v>0.2721</v>
+        <v>0.2629</v>
       </c>
     </row>
     <row r="11">
@@ -1279,13 +1279,13 @@
         <v>有色ETF</v>
       </c>
       <c r="C11" s="1">
-        <v>883.2</v>
+        <v>882.8</v>
       </c>
       <c r="D11" s="1">
-        <v>14.8</v>
+        <v>14.4</v>
       </c>
       <c r="E11" s="2">
-        <v>0.017</v>
+        <v>0.0166</v>
       </c>
       <c r="F11" t="str">
         <v/>
@@ -1300,25 +1300,25 @@
         <v/>
       </c>
       <c r="J11" s="1">
-        <v>22.7</v>
+        <v>22.3</v>
       </c>
       <c r="K11" s="2">
-        <v>0.0264</v>
+        <v>0.0259</v>
       </c>
       <c r="L11" s="1">
-        <v>22.7</v>
+        <v>22.3</v>
       </c>
       <c r="M11" s="2">
-        <v>0.0264</v>
+        <v>0.0259</v>
       </c>
       <c r="N11" s="1">
-        <v>22.7</v>
+        <v>22.3</v>
       </c>
       <c r="O11" s="1">
-        <v>23.5</v>
+        <v>22.3</v>
       </c>
       <c r="P11" s="1">
-        <v>23.5</v>
+        <v>22.3</v>
       </c>
       <c r="Q11" s="2">
         <v>0.0296</v>
@@ -1330,10 +1330,10 @@
         <v>3</v>
       </c>
       <c r="T11" s="2">
-        <v>0.017</v>
+        <v>0.0166</v>
       </c>
       <c r="U11" s="5">
-        <v>2.208</v>
+        <v>2.207</v>
       </c>
       <c r="V11" s="5">
         <v>2.151</v>
@@ -1342,16 +1342,16 @@
         <v/>
       </c>
       <c r="X11" s="2">
-        <v>0.0813</v>
+        <v>0.0808</v>
       </c>
       <c r="Y11" s="2">
-        <v>0.0475</v>
+        <v>0.047</v>
       </c>
       <c r="Z11" s="2">
-        <v>0.2125</v>
+        <v>0.212</v>
       </c>
       <c r="AA11" s="2">
-        <v>0.3182</v>
+        <v>0.3176</v>
       </c>
     </row>
     <row r="12">
@@ -1362,13 +1362,13 @@
         <v/>
       </c>
       <c r="C12" s="1">
-        <v>29781.2</v>
+        <v>29848</v>
       </c>
       <c r="D12" s="1">
-        <v>12.1</v>
+        <v>78.9</v>
       </c>
       <c r="E12" s="2">
-        <v>0.0004</v>
+        <v>0.0026</v>
       </c>
       <c r="F12" t="str">
         <v/>
@@ -1383,10 +1383,10 @@
         <v/>
       </c>
       <c r="J12" s="1">
-        <v>-210.59</v>
+        <v>-143.79</v>
       </c>
       <c r="K12" s="2">
-        <v>-0.007</v>
+        <v>-0.0048</v>
       </c>
       <c r="L12" t="str">
         <v/>
@@ -1395,13 +1395,13 @@
         <v/>
       </c>
       <c r="N12" s="1">
-        <v>-233.29</v>
+        <v>-146.69</v>
       </c>
       <c r="O12" s="1">
-        <v>-221.19</v>
+        <v>-146.69</v>
       </c>
       <c r="P12" s="1">
-        <v>-221.19</v>
+        <v>-146.69</v>
       </c>
       <c r="Q12" s="2">
         <v>0.9997</v>

--- a/20260513_银河.xlsx
+++ b/20260513_银河.xlsx
@@ -565,13 +565,13 @@
         <v>0.0094</v>
       </c>
       <c r="N2" s="1">
-        <v>5.9</v>
+        <v>7.1</v>
       </c>
       <c r="O2" s="1">
-        <v>5.9</v>
+        <v>7.1</v>
       </c>
       <c r="P2" s="1">
-        <v>5.9</v>
+        <v>7.1</v>
       </c>
       <c r="Q2" s="2">
         <v>0.024</v>
@@ -615,13 +615,13 @@
         <v>豆粕ETF</v>
       </c>
       <c r="C3" s="1">
-        <v>862.8</v>
+        <v>864</v>
       </c>
       <c r="D3" s="1">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="E3" s="2">
-        <v>0.0009</v>
+        <v>0.0023</v>
       </c>
       <c r="F3" t="str">
         <v/>
@@ -636,25 +636,25 @@
         <v/>
       </c>
       <c r="J3" s="1">
-        <v>-0.1</v>
+        <v>1.1</v>
       </c>
       <c r="K3" s="2">
-        <v>-0.0001</v>
+        <v>0.0013</v>
       </c>
       <c r="L3" s="1">
-        <v>-0.1</v>
+        <v>1.1</v>
       </c>
       <c r="M3" s="2">
-        <v>-0.0001</v>
+        <v>0.0013</v>
       </c>
       <c r="N3" s="1">
-        <v>-0.9</v>
+        <v>1.1</v>
       </c>
       <c r="O3" s="1">
-        <v>-0.9</v>
+        <v>1.1</v>
       </c>
       <c r="P3" s="1">
-        <v>-0.9</v>
+        <v>1.1</v>
       </c>
       <c r="Q3" s="2">
         <v>0.0289</v>
@@ -666,10 +666,10 @@
         <v>3</v>
       </c>
       <c r="T3" s="2">
-        <v>0.0009</v>
+        <v>0.0023</v>
       </c>
       <c r="U3" s="5">
-        <v>2.157</v>
+        <v>2.16</v>
       </c>
       <c r="V3" s="5">
         <v>2.157</v>
@@ -678,16 +678,16 @@
         <v/>
       </c>
       <c r="X3" s="2">
-        <v>0.0361</v>
+        <v>0.0375</v>
       </c>
       <c r="Y3" s="2">
-        <v>0.0845</v>
+        <v>0.086</v>
       </c>
       <c r="Z3" s="2">
-        <v>0.0921</v>
+        <v>0.0936</v>
       </c>
       <c r="AA3" s="2">
-        <v>0.1299</v>
+        <v>0.1315</v>
       </c>
     </row>
     <row r="4">
@@ -698,13 +698,13 @@
         <v>港股科技</v>
       </c>
       <c r="C4" s="1">
-        <v>734.8</v>
+        <v>732.6</v>
       </c>
       <c r="D4" s="1">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="E4" s="2">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="F4" t="str">
         <v/>
@@ -719,28 +719,28 @@
         <v/>
       </c>
       <c r="J4" s="1">
-        <v>-2.3</v>
+        <v>-4.5</v>
       </c>
       <c r="K4" s="2">
-        <v>-0.0031</v>
+        <v>-0.0061</v>
       </c>
       <c r="L4" s="1">
-        <v>-2.3</v>
+        <v>-4.5</v>
       </c>
       <c r="M4" s="2">
-        <v>-0.0031</v>
+        <v>-0.0061</v>
       </c>
       <c r="N4" s="1">
-        <v>-2.3</v>
+        <v>-3.4</v>
       </c>
       <c r="O4" s="1">
-        <v>-2.3</v>
+        <v>-3.4</v>
       </c>
       <c r="P4" s="1">
-        <v>-2.3</v>
+        <v>-3.4</v>
       </c>
       <c r="Q4" s="2">
-        <v>0.0246</v>
+        <v>0.0245</v>
       </c>
       <c r="R4" s="3">
         <v>1100</v>
@@ -749,28 +749,28 @@
         <v>3</v>
       </c>
       <c r="T4" s="2">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="U4" s="5">
-        <v>0.668</v>
+        <v>0.666</v>
       </c>
       <c r="V4" s="5">
         <v>0.67</v>
       </c>
       <c r="W4" s="2">
-        <v>0.003</v>
+        <v>0.006</v>
       </c>
       <c r="X4" s="2">
-        <v>0.0405</v>
+        <v>0.0374</v>
       </c>
       <c r="Y4" s="2">
-        <v>-0.0798</v>
+        <v>-0.0826</v>
       </c>
       <c r="Z4" s="2">
-        <v>-0.1864</v>
+        <v>-0.1888</v>
       </c>
       <c r="AA4" s="2">
-        <v>-0.0973</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="5">
@@ -781,13 +781,13 @@
         <v>300ETF</v>
       </c>
       <c r="C5" s="1">
-        <v>997.4</v>
+        <v>999</v>
       </c>
       <c r="D5" s="1">
-        <v>4.8</v>
+        <v>6.4</v>
       </c>
       <c r="E5" s="2">
-        <v>0.0048</v>
+        <v>0.0064</v>
       </c>
       <c r="F5" t="str">
         <v/>
@@ -802,25 +802,25 @@
         <v/>
       </c>
       <c r="J5" s="1">
-        <v>6.1</v>
+        <v>7.7</v>
       </c>
       <c r="K5" s="2">
-        <v>0.0062</v>
+        <v>0.0078</v>
       </c>
       <c r="L5" s="1">
-        <v>6.1</v>
+        <v>7.7</v>
       </c>
       <c r="M5" s="2">
-        <v>0.0062</v>
+        <v>0.0078</v>
       </c>
       <c r="N5" s="1">
-        <v>5.9</v>
+        <v>6.5</v>
       </c>
       <c r="O5" s="1">
-        <v>5.9</v>
+        <v>6.5</v>
       </c>
       <c r="P5" s="1">
-        <v>5.9</v>
+        <v>6.5</v>
       </c>
       <c r="Q5" s="2">
         <v>0.0334</v>
@@ -832,10 +832,10 @@
         <v>3</v>
       </c>
       <c r="T5" s="2">
-        <v>0.0048</v>
+        <v>0.0064</v>
       </c>
       <c r="U5" s="5">
-        <v>4.987</v>
+        <v>4.995</v>
       </c>
       <c r="V5" s="5">
         <v>4.957</v>
@@ -844,16 +844,16 @@
         <v/>
       </c>
       <c r="X5" s="2">
-        <v>0.0744</v>
+        <v>0.0761</v>
       </c>
       <c r="Y5" s="2">
-        <v>0.055</v>
+        <v>0.0567</v>
       </c>
       <c r="Z5" s="2">
-        <v>0.0738</v>
+        <v>0.0755</v>
       </c>
       <c r="AA5" s="2">
-        <v>0.3113</v>
+        <v>0.3134</v>
       </c>
     </row>
     <row r="6">
@@ -864,13 +864,13 @@
         <v>黄金ETF</v>
       </c>
       <c r="C6" s="1">
-        <v>979.9</v>
+        <v>982.3</v>
       </c>
       <c r="D6" s="1">
-        <v>-0.7</v>
+        <v>1.7</v>
       </c>
       <c r="E6" s="2">
-        <v>-0.0007</v>
+        <v>0.0017</v>
       </c>
       <c r="F6" t="str">
         <v/>
@@ -885,28 +885,28 @@
         <v/>
       </c>
       <c r="J6" s="1">
-        <v>6.2</v>
+        <v>8.6</v>
       </c>
       <c r="K6" s="2">
-        <v>0.0064</v>
+        <v>0.0088</v>
       </c>
       <c r="L6" s="1">
-        <v>6.2</v>
+        <v>8.6</v>
       </c>
       <c r="M6" s="2">
-        <v>0.0064</v>
+        <v>0.0088</v>
       </c>
       <c r="N6" s="1">
-        <v>6.1</v>
+        <v>6.9</v>
       </c>
       <c r="O6" s="1">
-        <v>6.1</v>
+        <v>6.9</v>
       </c>
       <c r="P6" s="1">
-        <v>6.1</v>
+        <v>6.9</v>
       </c>
       <c r="Q6" s="2">
-        <v>0.0328</v>
+        <v>0.0329</v>
       </c>
       <c r="R6" s="3">
         <v>100</v>
@@ -915,10 +915,10 @@
         <v>3</v>
       </c>
       <c r="T6" s="2">
-        <v>-0.0007</v>
+        <v>0.0017</v>
       </c>
       <c r="U6" s="5">
-        <v>9.799</v>
+        <v>9.823</v>
       </c>
       <c r="V6" s="5">
         <v>9.737</v>
@@ -927,16 +927,16 @@
         <v/>
       </c>
       <c r="X6" s="2">
-        <v>-0.0173</v>
+        <v>-0.0149</v>
       </c>
       <c r="Y6" s="2">
-        <v>-0.086</v>
+        <v>-0.0837</v>
       </c>
       <c r="Z6" s="2">
-        <v>0.0853</v>
+        <v>0.088</v>
       </c>
       <c r="AA6" s="2">
-        <v>0.3285</v>
+        <v>0.3317</v>
       </c>
     </row>
     <row r="7">
@@ -989,7 +989,7 @@
         <v>2.55</v>
       </c>
       <c r="Q7" s="2">
-        <v>0.1012</v>
+        <v>0.1011</v>
       </c>
       <c r="R7" s="3">
         <v>2700</v>
@@ -1030,13 +1030,13 @@
         <v>创业板</v>
       </c>
       <c r="C8" s="1">
-        <v>803.2</v>
+        <v>805</v>
       </c>
       <c r="D8" s="1">
-        <v>15.2</v>
+        <v>17</v>
       </c>
       <c r="E8" s="2">
-        <v>0.0193</v>
+        <v>0.0216</v>
       </c>
       <c r="F8" t="str">
         <v/>
@@ -1051,25 +1051,25 @@
         <v/>
       </c>
       <c r="J8" s="1">
-        <v>16.5</v>
+        <v>18.3</v>
       </c>
       <c r="K8" s="2">
-        <v>0.021</v>
+        <v>0.0233</v>
       </c>
       <c r="L8" s="1">
-        <v>16.5</v>
+        <v>18.3</v>
       </c>
       <c r="M8" s="2">
-        <v>0.021</v>
+        <v>0.0233</v>
       </c>
       <c r="N8" s="1">
-        <v>15.1</v>
+        <v>17.3</v>
       </c>
       <c r="O8" s="1">
-        <v>15.1</v>
+        <v>17.3</v>
       </c>
       <c r="P8" s="1">
-        <v>15.1</v>
+        <v>17.3</v>
       </c>
       <c r="Q8" s="2">
         <v>0.0269</v>
@@ -1081,10 +1081,10 @@
         <v>3</v>
       </c>
       <c r="T8" s="2">
-        <v>0.0193</v>
+        <v>0.0216</v>
       </c>
       <c r="U8" s="5">
-        <v>4.016</v>
+        <v>4.025</v>
       </c>
       <c r="V8" s="5">
         <v>3.934</v>
@@ -1093,16 +1093,16 @@
         <v/>
       </c>
       <c r="X8" s="2">
-        <v>0.1684</v>
+        <v>0.171</v>
       </c>
       <c r="Y8" s="2">
-        <v>0.21</v>
+        <v>0.2127</v>
       </c>
       <c r="Z8" s="2">
-        <v>0.2922</v>
+        <v>0.295</v>
       </c>
       <c r="AA8" s="2">
-        <v>0.9715</v>
+        <v>0.9759</v>
       </c>
     </row>
     <row r="9">
@@ -1113,13 +1113,13 @@
         <v>转债ETF</v>
       </c>
       <c r="C9" s="1">
-        <v>20190.8</v>
+        <v>20197.8</v>
       </c>
       <c r="D9" s="1">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="E9" s="2">
-        <v>0.0021</v>
+        <v>0.0024</v>
       </c>
       <c r="F9" t="str">
         <v/>
@@ -1134,28 +1134,28 @@
         <v/>
       </c>
       <c r="J9" s="1">
-        <v>-186.84</v>
+        <v>-179.84</v>
       </c>
       <c r="K9" s="2">
-        <v>-0.0092</v>
+        <v>-0.0088</v>
       </c>
       <c r="L9" s="1">
-        <v>-186.84</v>
+        <v>-179.84</v>
       </c>
       <c r="M9" s="2">
-        <v>-0.0092</v>
+        <v>-0.0088</v>
       </c>
       <c r="N9" s="1">
-        <v>-186.84</v>
+        <v>-179.84</v>
       </c>
       <c r="O9" s="1">
-        <v>-186.84</v>
+        <v>-179.84</v>
       </c>
       <c r="P9" s="1">
-        <v>-186.84</v>
+        <v>-179.84</v>
       </c>
       <c r="Q9" s="2">
-        <v>0.6763</v>
+        <v>0.6762</v>
       </c>
       <c r="R9" s="3">
         <v>1400</v>
@@ -1164,28 +1164,28 @@
         <v>3</v>
       </c>
       <c r="T9" s="2">
-        <v>0.0021</v>
+        <v>0.0024</v>
       </c>
       <c r="U9" s="5">
-        <v>14.422</v>
+        <v>14.427</v>
       </c>
       <c r="V9" s="5">
         <v>14.555</v>
       </c>
       <c r="W9" s="2">
-        <v>0.0092</v>
+        <v>0.0089</v>
       </c>
       <c r="X9" s="2">
-        <v>0.0316</v>
+        <v>0.032</v>
       </c>
       <c r="Y9" s="2">
-        <v>-0.0188</v>
+        <v>-0.0184</v>
       </c>
       <c r="Z9" s="2">
-        <v>0.06</v>
+        <v>0.0604</v>
       </c>
       <c r="AA9" s="2">
-        <v>0.1982</v>
+        <v>0.1986</v>
       </c>
     </row>
     <row r="10">
@@ -1279,13 +1279,13 @@
         <v>有色ETF</v>
       </c>
       <c r="C11" s="1">
-        <v>882.8</v>
+        <v>886</v>
       </c>
       <c r="D11" s="1">
-        <v>14.4</v>
+        <v>17.6</v>
       </c>
       <c r="E11" s="2">
-        <v>0.0166</v>
+        <v>0.0203</v>
       </c>
       <c r="F11" t="str">
         <v/>
@@ -1300,28 +1300,28 @@
         <v/>
       </c>
       <c r="J11" s="1">
-        <v>22.3</v>
+        <v>25.5</v>
       </c>
       <c r="K11" s="2">
-        <v>0.0259</v>
+        <v>0.0296</v>
       </c>
       <c r="L11" s="1">
-        <v>22.3</v>
+        <v>25.5</v>
       </c>
       <c r="M11" s="2">
-        <v>0.0259</v>
+        <v>0.0296</v>
       </c>
       <c r="N11" s="1">
-        <v>22.3</v>
+        <v>23.1</v>
       </c>
       <c r="O11" s="1">
-        <v>22.3</v>
+        <v>23.1</v>
       </c>
       <c r="P11" s="1">
-        <v>22.3</v>
+        <v>23.1</v>
       </c>
       <c r="Q11" s="2">
-        <v>0.0296</v>
+        <v>0.0297</v>
       </c>
       <c r="R11" s="3">
         <v>400</v>
@@ -1330,10 +1330,10 @@
         <v>3</v>
       </c>
       <c r="T11" s="2">
-        <v>0.0166</v>
+        <v>0.0203</v>
       </c>
       <c r="U11" s="5">
-        <v>2.207</v>
+        <v>2.215</v>
       </c>
       <c r="V11" s="5">
         <v>2.151</v>
@@ -1342,16 +1342,16 @@
         <v/>
       </c>
       <c r="X11" s="2">
-        <v>0.0808</v>
+        <v>0.0847</v>
       </c>
       <c r="Y11" s="2">
-        <v>0.047</v>
+        <v>0.0508</v>
       </c>
       <c r="Z11" s="2">
-        <v>0.212</v>
+        <v>0.2164</v>
       </c>
       <c r="AA11" s="2">
-        <v>0.3176</v>
+        <v>0.3224</v>
       </c>
     </row>
     <row r="12">
@@ -1362,13 +1362,13 @@
         <v/>
       </c>
       <c r="C12" s="1">
-        <v>29848</v>
+        <v>29863</v>
       </c>
       <c r="D12" s="1">
-        <v>78.9</v>
+        <v>93.9</v>
       </c>
       <c r="E12" s="2">
-        <v>0.0026</v>
+        <v>0.0032</v>
       </c>
       <c r="F12" t="str">
         <v/>
@@ -1383,10 +1383,10 @@
         <v/>
       </c>
       <c r="J12" s="1">
-        <v>-143.79</v>
+        <v>-128.79</v>
       </c>
       <c r="K12" s="2">
-        <v>-0.0048</v>
+        <v>-0.0043</v>
       </c>
       <c r="L12" t="str">
         <v/>
@@ -1395,13 +1395,13 @@
         <v/>
       </c>
       <c r="N12" s="1">
-        <v>-146.69</v>
+        <v>-133.19</v>
       </c>
       <c r="O12" s="1">
-        <v>-146.69</v>
+        <v>-133.19</v>
       </c>
       <c r="P12" s="1">
-        <v>-146.69</v>
+        <v>-133.19</v>
       </c>
       <c r="Q12" s="2">
         <v>0.9997</v>

--- a/20260513_银河.xlsx
+++ b/20260513_银河.xlsx
@@ -532,13 +532,13 @@
         <v>1000ETF</v>
       </c>
       <c r="C2" s="1">
-        <v>717.8</v>
+        <v>719.6</v>
       </c>
       <c r="D2" s="1">
-        <v>9.8</v>
+        <v>11.6</v>
       </c>
       <c r="E2" s="2">
-        <v>0.0138</v>
+        <v>0.0164</v>
       </c>
       <c r="F2" t="str">
         <v/>
@@ -553,28 +553,28 @@
         <v/>
       </c>
       <c r="J2" s="1">
-        <v>6.7</v>
+        <v>8.5</v>
       </c>
       <c r="K2" s="2">
-        <v>0.0094</v>
+        <v>0.012</v>
       </c>
       <c r="L2" s="1">
-        <v>6.7</v>
+        <v>8.5</v>
       </c>
       <c r="M2" s="2">
-        <v>0.0094</v>
+        <v>0.012</v>
       </c>
       <c r="N2" s="1">
-        <v>7.1</v>
+        <v>8.5</v>
       </c>
       <c r="O2" s="1">
-        <v>7.1</v>
+        <v>8.5</v>
       </c>
       <c r="P2" s="1">
-        <v>7.1</v>
+        <v>8.5</v>
       </c>
       <c r="Q2" s="2">
-        <v>0.024</v>
+        <v>0.0241</v>
       </c>
       <c r="R2" s="3">
         <v>200</v>
@@ -583,10 +583,10 @@
         <v>3</v>
       </c>
       <c r="T2" s="2">
-        <v>0.0138</v>
+        <v>0.0164</v>
       </c>
       <c r="U2" s="5">
-        <v>3.589</v>
+        <v>3.598</v>
       </c>
       <c r="V2" s="5">
         <v>3.556</v>
@@ -595,16 +595,16 @@
         <v/>
       </c>
       <c r="X2" s="2">
-        <v>0.1212</v>
+        <v>0.124</v>
       </c>
       <c r="Y2" s="2">
-        <v>0.0759</v>
+        <v>0.0786</v>
       </c>
       <c r="Z2" s="2">
-        <v>0.1977</v>
+        <v>0.2007</v>
       </c>
       <c r="AA2" s="2">
-        <v>0.4705</v>
+        <v>0.4742</v>
       </c>
     </row>
     <row r="3">
@@ -615,13 +615,13 @@
         <v>豆粕ETF</v>
       </c>
       <c r="C3" s="1">
-        <v>864</v>
+        <v>864.4</v>
       </c>
       <c r="D3" s="1">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="E3" s="2">
-        <v>0.0023</v>
+        <v>0.0028</v>
       </c>
       <c r="F3" t="str">
         <v/>
@@ -636,25 +636,25 @@
         <v/>
       </c>
       <c r="J3" s="1">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="K3" s="2">
-        <v>0.0013</v>
+        <v>0.0017</v>
       </c>
       <c r="L3" s="1">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="M3" s="2">
-        <v>0.0013</v>
+        <v>0.0017</v>
       </c>
       <c r="N3" s="1">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="O3" s="1">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="P3" s="1">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="Q3" s="2">
         <v>0.0289</v>
@@ -666,10 +666,10 @@
         <v>3</v>
       </c>
       <c r="T3" s="2">
-        <v>0.0023</v>
+        <v>0.0028</v>
       </c>
       <c r="U3" s="5">
-        <v>2.16</v>
+        <v>2.161</v>
       </c>
       <c r="V3" s="5">
         <v>2.157</v>
@@ -678,16 +678,16 @@
         <v/>
       </c>
       <c r="X3" s="2">
-        <v>0.0375</v>
+        <v>0.038</v>
       </c>
       <c r="Y3" s="2">
-        <v>0.086</v>
+        <v>0.0865</v>
       </c>
       <c r="Z3" s="2">
-        <v>0.0936</v>
+        <v>0.0941</v>
       </c>
       <c r="AA3" s="2">
-        <v>0.1315</v>
+        <v>0.132</v>
       </c>
     </row>
     <row r="4">
@@ -698,13 +698,13 @@
         <v>港股科技</v>
       </c>
       <c r="C4" s="1">
-        <v>732.6</v>
+        <v>734.8</v>
       </c>
       <c r="D4" s="1">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="E4" s="2">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="F4" t="str">
         <v/>
@@ -719,28 +719,28 @@
         <v/>
       </c>
       <c r="J4" s="1">
-        <v>-4.5</v>
+        <v>-2.3</v>
       </c>
       <c r="K4" s="2">
-        <v>-0.0061</v>
+        <v>-0.0031</v>
       </c>
       <c r="L4" s="1">
-        <v>-4.5</v>
+        <v>-2.3</v>
       </c>
       <c r="M4" s="2">
-        <v>-0.0061</v>
+        <v>-0.0031</v>
       </c>
       <c r="N4" s="1">
-        <v>-3.4</v>
+        <v>-2.3</v>
       </c>
       <c r="O4" s="1">
-        <v>-3.4</v>
+        <v>-2.3</v>
       </c>
       <c r="P4" s="1">
-        <v>-3.4</v>
+        <v>-2.3</v>
       </c>
       <c r="Q4" s="2">
-        <v>0.0245</v>
+        <v>0.0246</v>
       </c>
       <c r="R4" s="3">
         <v>1100</v>
@@ -749,28 +749,28 @@
         <v>3</v>
       </c>
       <c r="T4" s="2">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="U4" s="5">
-        <v>0.666</v>
+        <v>0.668</v>
       </c>
       <c r="V4" s="5">
         <v>0.67</v>
       </c>
       <c r="W4" s="2">
-        <v>0.006</v>
+        <v>0.003</v>
       </c>
       <c r="X4" s="2">
-        <v>0.0374</v>
+        <v>0.0405</v>
       </c>
       <c r="Y4" s="2">
-        <v>-0.0826</v>
+        <v>-0.0798</v>
       </c>
       <c r="Z4" s="2">
-        <v>-0.1888</v>
+        <v>-0.1864</v>
       </c>
       <c r="AA4" s="2">
-        <v>-0.1</v>
+        <v>-0.0973</v>
       </c>
     </row>
     <row r="5">
@@ -781,13 +781,13 @@
         <v>300ETF</v>
       </c>
       <c r="C5" s="1">
-        <v>999</v>
+        <v>1003.4</v>
       </c>
       <c r="D5" s="1">
-        <v>6.4</v>
+        <v>10.8</v>
       </c>
       <c r="E5" s="2">
-        <v>0.0064</v>
+        <v>0.0109</v>
       </c>
       <c r="F5" t="str">
         <v/>
@@ -802,28 +802,28 @@
         <v/>
       </c>
       <c r="J5" s="1">
-        <v>7.7</v>
+        <v>12.1</v>
       </c>
       <c r="K5" s="2">
-        <v>0.0078</v>
+        <v>0.0122</v>
       </c>
       <c r="L5" s="1">
-        <v>7.7</v>
+        <v>12.1</v>
       </c>
       <c r="M5" s="2">
-        <v>0.0078</v>
+        <v>0.0122</v>
       </c>
       <c r="N5" s="1">
-        <v>6.5</v>
+        <v>12.1</v>
       </c>
       <c r="O5" s="1">
-        <v>6.5</v>
+        <v>12.1</v>
       </c>
       <c r="P5" s="1">
-        <v>6.5</v>
+        <v>12.1</v>
       </c>
       <c r="Q5" s="2">
-        <v>0.0334</v>
+        <v>0.0336</v>
       </c>
       <c r="R5" s="3">
         <v>200</v>
@@ -832,10 +832,10 @@
         <v>3</v>
       </c>
       <c r="T5" s="2">
-        <v>0.0064</v>
+        <v>0.0109</v>
       </c>
       <c r="U5" s="5">
-        <v>4.995</v>
+        <v>5.017</v>
       </c>
       <c r="V5" s="5">
         <v>4.957</v>
@@ -844,16 +844,16 @@
         <v/>
       </c>
       <c r="X5" s="2">
-        <v>0.0761</v>
+        <v>0.0808</v>
       </c>
       <c r="Y5" s="2">
-        <v>0.0567</v>
+        <v>0.0613</v>
       </c>
       <c r="Z5" s="2">
-        <v>0.0755</v>
+        <v>0.0802</v>
       </c>
       <c r="AA5" s="2">
-        <v>0.3134</v>
+        <v>0.3192</v>
       </c>
     </row>
     <row r="6">
@@ -864,13 +864,13 @@
         <v>黄金ETF</v>
       </c>
       <c r="C6" s="1">
-        <v>982.3</v>
+        <v>980.4</v>
       </c>
       <c r="D6" s="1">
-        <v>1.7</v>
+        <v>-0.2</v>
       </c>
       <c r="E6" s="2">
-        <v>0.0017</v>
+        <v>-0.0002</v>
       </c>
       <c r="F6" t="str">
         <v/>
@@ -885,28 +885,28 @@
         <v/>
       </c>
       <c r="J6" s="1">
-        <v>8.6</v>
+        <v>6.7</v>
       </c>
       <c r="K6" s="2">
-        <v>0.0088</v>
+        <v>0.0069</v>
       </c>
       <c r="L6" s="1">
-        <v>8.6</v>
+        <v>6.7</v>
       </c>
       <c r="M6" s="2">
-        <v>0.0088</v>
+        <v>0.0069</v>
       </c>
       <c r="N6" s="1">
-        <v>6.9</v>
+        <v>6.7</v>
       </c>
       <c r="O6" s="1">
-        <v>6.9</v>
+        <v>6.7</v>
       </c>
       <c r="P6" s="1">
-        <v>6.9</v>
+        <v>6.7</v>
       </c>
       <c r="Q6" s="2">
-        <v>0.0329</v>
+        <v>0.0328</v>
       </c>
       <c r="R6" s="3">
         <v>100</v>
@@ -915,10 +915,10 @@
         <v>3</v>
       </c>
       <c r="T6" s="2">
-        <v>0.0017</v>
+        <v>-0.0002</v>
       </c>
       <c r="U6" s="5">
-        <v>9.823</v>
+        <v>9.804</v>
       </c>
       <c r="V6" s="5">
         <v>9.737</v>
@@ -927,16 +927,16 @@
         <v/>
       </c>
       <c r="X6" s="2">
-        <v>-0.0149</v>
+        <v>-0.0168</v>
       </c>
       <c r="Y6" s="2">
-        <v>-0.0837</v>
+        <v>-0.0855</v>
       </c>
       <c r="Z6" s="2">
-        <v>0.088</v>
+        <v>0.0859</v>
       </c>
       <c r="AA6" s="2">
-        <v>0.3317</v>
+        <v>0.3291</v>
       </c>
     </row>
     <row r="7">
@@ -989,7 +989,7 @@
         <v>2.55</v>
       </c>
       <c r="Q7" s="2">
-        <v>0.1011</v>
+        <v>0.101</v>
       </c>
       <c r="R7" s="3">
         <v>2700</v>
@@ -1030,13 +1030,13 @@
         <v>创业板</v>
       </c>
       <c r="C8" s="1">
-        <v>805</v>
+        <v>809.6</v>
       </c>
       <c r="D8" s="1">
-        <v>17</v>
+        <v>21.6</v>
       </c>
       <c r="E8" s="2">
-        <v>0.0216</v>
+        <v>0.0274</v>
       </c>
       <c r="F8" t="str">
         <v/>
@@ -1051,28 +1051,28 @@
         <v/>
       </c>
       <c r="J8" s="1">
-        <v>18.3</v>
+        <v>22.9</v>
       </c>
       <c r="K8" s="2">
-        <v>0.0233</v>
+        <v>0.0291</v>
       </c>
       <c r="L8" s="1">
-        <v>18.3</v>
+        <v>22.9</v>
       </c>
       <c r="M8" s="2">
-        <v>0.0233</v>
+        <v>0.0291</v>
       </c>
       <c r="N8" s="1">
-        <v>17.3</v>
+        <v>22.9</v>
       </c>
       <c r="O8" s="1">
-        <v>17.3</v>
+        <v>22.9</v>
       </c>
       <c r="P8" s="1">
-        <v>17.3</v>
+        <v>22.9</v>
       </c>
       <c r="Q8" s="2">
-        <v>0.0269</v>
+        <v>0.0271</v>
       </c>
       <c r="R8" s="3">
         <v>200</v>
@@ -1081,10 +1081,10 @@
         <v>3</v>
       </c>
       <c r="T8" s="2">
-        <v>0.0216</v>
+        <v>0.0274</v>
       </c>
       <c r="U8" s="5">
-        <v>4.025</v>
+        <v>4.048</v>
       </c>
       <c r="V8" s="5">
         <v>3.934</v>
@@ -1093,16 +1093,16 @@
         <v/>
       </c>
       <c r="X8" s="2">
-        <v>0.171</v>
+        <v>0.1777</v>
       </c>
       <c r="Y8" s="2">
-        <v>0.2127</v>
+        <v>0.2196</v>
       </c>
       <c r="Z8" s="2">
-        <v>0.295</v>
+        <v>0.3024</v>
       </c>
       <c r="AA8" s="2">
-        <v>0.9759</v>
+        <v>0.9872</v>
       </c>
     </row>
     <row r="9">
@@ -1113,13 +1113,13 @@
         <v>转债ETF</v>
       </c>
       <c r="C9" s="1">
-        <v>20197.8</v>
+        <v>20220.2</v>
       </c>
       <c r="D9" s="1">
-        <v>49</v>
+        <v>71.4</v>
       </c>
       <c r="E9" s="2">
-        <v>0.0024</v>
+        <v>0.0035</v>
       </c>
       <c r="F9" t="str">
         <v/>
@@ -1134,28 +1134,28 @@
         <v/>
       </c>
       <c r="J9" s="1">
-        <v>-179.84</v>
+        <v>-157.44</v>
       </c>
       <c r="K9" s="2">
-        <v>-0.0088</v>
+        <v>-0.0077</v>
       </c>
       <c r="L9" s="1">
-        <v>-179.84</v>
+        <v>-157.44</v>
       </c>
       <c r="M9" s="2">
-        <v>-0.0088</v>
+        <v>-0.0077</v>
       </c>
       <c r="N9" s="1">
-        <v>-179.84</v>
+        <v>-157.44</v>
       </c>
       <c r="O9" s="1">
-        <v>-179.84</v>
+        <v>-157.44</v>
       </c>
       <c r="P9" s="1">
-        <v>-179.84</v>
+        <v>-157.44</v>
       </c>
       <c r="Q9" s="2">
-        <v>0.6762</v>
+        <v>0.6761</v>
       </c>
       <c r="R9" s="3">
         <v>1400</v>
@@ -1164,28 +1164,28 @@
         <v>3</v>
       </c>
       <c r="T9" s="2">
-        <v>0.0024</v>
+        <v>0.0035</v>
       </c>
       <c r="U9" s="5">
-        <v>14.427</v>
+        <v>14.443</v>
       </c>
       <c r="V9" s="5">
         <v>14.555</v>
       </c>
       <c r="W9" s="2">
-        <v>0.0089</v>
+        <v>0.0078</v>
       </c>
       <c r="X9" s="2">
-        <v>0.032</v>
+        <v>0.0331</v>
       </c>
       <c r="Y9" s="2">
-        <v>-0.0184</v>
+        <v>-0.0173</v>
       </c>
       <c r="Z9" s="2">
-        <v>0.0604</v>
+        <v>0.0615</v>
       </c>
       <c r="AA9" s="2">
-        <v>0.1986</v>
+        <v>0.1999</v>
       </c>
     </row>
     <row r="10">
@@ -1196,13 +1196,13 @@
         <v>能源化工</v>
       </c>
       <c r="C10" s="1">
-        <v>657.2</v>
+        <v>660</v>
       </c>
       <c r="D10" s="1">
-        <v>-9.6</v>
+        <v>-6.8</v>
       </c>
       <c r="E10" s="2">
-        <v>-0.0144</v>
+        <v>-0.0102</v>
       </c>
       <c r="F10" t="str">
         <v/>
@@ -1217,28 +1217,28 @@
         <v/>
       </c>
       <c r="J10" s="1">
-        <v>-14.9</v>
+        <v>-12.1</v>
       </c>
       <c r="K10" s="2">
-        <v>-0.0222</v>
+        <v>-0.018</v>
       </c>
       <c r="L10" s="1">
-        <v>-14.9</v>
+        <v>-12.1</v>
       </c>
       <c r="M10" s="2">
-        <v>-0.0222</v>
+        <v>-0.018</v>
       </c>
       <c r="N10" s="1">
-        <v>-14.5</v>
+        <v>-12.1</v>
       </c>
       <c r="O10" s="1">
-        <v>-14.5</v>
+        <v>-12.1</v>
       </c>
       <c r="P10" s="1">
-        <v>-14.5</v>
+        <v>-12.1</v>
       </c>
       <c r="Q10" s="2">
-        <v>0.022</v>
+        <v>0.0221</v>
       </c>
       <c r="R10" s="3">
         <v>400</v>
@@ -1247,28 +1247,28 @@
         <v>3</v>
       </c>
       <c r="T10" s="2">
-        <v>-0.0144</v>
+        <v>-0.0102</v>
       </c>
       <c r="U10" s="5">
-        <v>1.643</v>
+        <v>1.65</v>
       </c>
       <c r="V10" s="5">
         <v>1.68</v>
       </c>
       <c r="W10" s="2">
-        <v>0.0225</v>
+        <v>0.0182</v>
       </c>
       <c r="X10" s="2">
-        <v>0.0173</v>
+        <v>0.0217</v>
       </c>
       <c r="Y10" s="2">
-        <v>0.2816</v>
+        <v>0.287</v>
       </c>
       <c r="Z10" s="2">
-        <v>0.3401</v>
+        <v>0.3458</v>
       </c>
       <c r="AA10" s="2">
-        <v>0.2629</v>
+        <v>0.2682</v>
       </c>
     </row>
     <row r="11">
@@ -1279,13 +1279,13 @@
         <v>有色ETF</v>
       </c>
       <c r="C11" s="1">
-        <v>886</v>
+        <v>884.4</v>
       </c>
       <c r="D11" s="1">
-        <v>17.6</v>
+        <v>16</v>
       </c>
       <c r="E11" s="2">
-        <v>0.0203</v>
+        <v>0.0184</v>
       </c>
       <c r="F11" t="str">
         <v/>
@@ -1300,28 +1300,28 @@
         <v/>
       </c>
       <c r="J11" s="1">
-        <v>25.5</v>
+        <v>23.9</v>
       </c>
       <c r="K11" s="2">
+        <v>0.0278</v>
+      </c>
+      <c r="L11" s="1">
+        <v>23.9</v>
+      </c>
+      <c r="M11" s="2">
+        <v>0.0278</v>
+      </c>
+      <c r="N11" s="1">
+        <v>23.9</v>
+      </c>
+      <c r="O11" s="1">
+        <v>23.9</v>
+      </c>
+      <c r="P11" s="1">
+        <v>23.9</v>
+      </c>
+      <c r="Q11" s="2">
         <v>0.0296</v>
-      </c>
-      <c r="L11" s="1">
-        <v>25.5</v>
-      </c>
-      <c r="M11" s="2">
-        <v>0.0296</v>
-      </c>
-      <c r="N11" s="1">
-        <v>23.1</v>
-      </c>
-      <c r="O11" s="1">
-        <v>23.1</v>
-      </c>
-      <c r="P11" s="1">
-        <v>23.1</v>
-      </c>
-      <c r="Q11" s="2">
-        <v>0.0297</v>
       </c>
       <c r="R11" s="3">
         <v>400</v>
@@ -1330,10 +1330,10 @@
         <v>3</v>
       </c>
       <c r="T11" s="2">
-        <v>0.0203</v>
+        <v>0.0184</v>
       </c>
       <c r="U11" s="5">
-        <v>2.215</v>
+        <v>2.211</v>
       </c>
       <c r="V11" s="5">
         <v>2.151</v>
@@ -1342,16 +1342,16 @@
         <v/>
       </c>
       <c r="X11" s="2">
-        <v>0.0847</v>
+        <v>0.0828</v>
       </c>
       <c r="Y11" s="2">
-        <v>0.0508</v>
+        <v>0.0489</v>
       </c>
       <c r="Z11" s="2">
-        <v>0.2164</v>
+        <v>0.2142</v>
       </c>
       <c r="AA11" s="2">
-        <v>0.3224</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="12">
@@ -1362,13 +1362,13 @@
         <v/>
       </c>
       <c r="C12" s="1">
-        <v>29863</v>
+        <v>29898.1</v>
       </c>
       <c r="D12" s="1">
-        <v>93.9</v>
+        <v>129</v>
       </c>
       <c r="E12" s="2">
-        <v>0.0032</v>
+        <v>0.0043</v>
       </c>
       <c r="F12" t="str">
         <v/>
@@ -1383,10 +1383,10 @@
         <v/>
       </c>
       <c r="J12" s="1">
-        <v>-128.79</v>
+        <v>-93.69</v>
       </c>
       <c r="K12" s="2">
-        <v>-0.0043</v>
+        <v>-0.0031</v>
       </c>
       <c r="L12" t="str">
         <v/>
@@ -1395,13 +1395,13 @@
         <v/>
       </c>
       <c r="N12" s="1">
-        <v>-133.19</v>
+        <v>-93.69</v>
       </c>
       <c r="O12" s="1">
-        <v>-133.19</v>
+        <v>-93.69</v>
       </c>
       <c r="P12" s="1">
-        <v>-133.19</v>
+        <v>-93.69</v>
       </c>
       <c r="Q12" s="2">
         <v>0.9997</v>
